--- a/l18n/lqa-textes-i18n.xlsx
+++ b/l18n/lqa-textes-i18n.xlsx
@@ -783,7 +783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -1136,7 +1136,7 @@
     <row r="22" ht="98" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1158,7 +1158,7 @@
     <row r="23" ht="98" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1180,7 +1180,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1266,47 +1266,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Suomi), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Orb asetettiin oudolle [color:65845]valtaistuimelle[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Mikä on suosikkivideopelisi, kerro meille miksi?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 sanaa</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1314,7 +1350,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1326,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -1679,7 +1715,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1701,7 +1737,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1723,7 +1759,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1745,7 +1781,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1767,7 +1803,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1789,7 +1825,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1809,47 +1845,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Español), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]El orbe fue colocado en un extraño [color:65845]trono[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>¿Cuál es tu videojuego favorito, cuéntanos por qué?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 palabras</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1857,7 +1929,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1869,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -2222,7 +2294,7 @@
     <row r="22" ht="70" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -2244,7 +2316,7 @@
     <row r="23" ht="70" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -2266,7 +2338,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2288,7 +2360,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -2310,7 +2382,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2332,7 +2404,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -2352,51 +2424,87 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Español), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]El orbe fue colocado en un extraño [color:65845]trono[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>¿Cuál es tu videojuego favorito, cuéntanos por qué?</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>⚠ Identical to es-ES — see note on the glossary/target text above.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 palabras</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2404,7 +2512,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2416,7 +2524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -2769,7 +2877,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -2791,7 +2899,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -2813,7 +2921,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2835,7 +2943,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -2857,7 +2965,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2879,7 +2987,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -2899,47 +3007,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Português), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]O orbe foi colocado num estranho [color:65845]trono[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Qual é o teu jogo de videojogos favorito, diz-nos porquê?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 palavras</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2947,7 +3091,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2959,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -3312,7 +3456,7 @@
     <row r="22" ht="56" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -3334,7 +3478,7 @@
     <row r="23" ht="56" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -3356,7 +3500,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -3378,7 +3522,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -3400,7 +3544,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -3422,7 +3566,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -3442,51 +3586,87 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Português), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]O orbe foi colocado em um estranho [color:65845]trono[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Qual é o seu videogame favorito, conte-nos porquê?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Good regional variant ('videogame' vs 'jogo de videojogos').</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 palavras</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3494,7 +3674,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3506,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -3859,7 +4039,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -3881,7 +4061,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -3903,7 +4083,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -3925,7 +4105,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -3947,7 +4127,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -3969,7 +4149,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -3989,47 +4169,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Русский), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Сфера была помещена на странный [color:65845]трон[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Какая ваша любимая видеоигра, расскажите почему?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 слов</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4037,7 +4253,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4049,7 +4265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -4424,7 +4640,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -4446,7 +4662,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -4468,7 +4684,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -4490,7 +4706,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -4512,7 +4728,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -4534,7 +4750,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -4554,55 +4770,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Polski), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Sfera została umieszczona na dziwnym [color:65845]tronie[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Jaka jest Twoja ulubiona gra wideo i dlaczego?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 słów</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4614,7 +4866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -4967,7 +5219,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -4989,7 +5241,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -5011,7 +5263,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -5033,7 +5285,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -5055,7 +5307,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -5077,7 +5329,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -5097,47 +5349,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Čeština), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Sféra byla umístěna na podivný [color:65845]trůn[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Jaká je vaše oblíbená videohra a proč?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 slov</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5145,7 +5433,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5157,7 +5445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -5510,7 +5798,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -5532,7 +5820,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -5554,7 +5842,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -5576,7 +5864,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -5598,7 +5886,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -5620,7 +5908,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -5640,47 +5928,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Magyar), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]A gömb egy különös [color:65845]trónra[/color] lett elhelyezve.[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Mi a kedvenc videojátékod, és miért?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 szó</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5688,7 +6012,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5700,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -6053,7 +6377,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6075,7 +6399,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -6097,7 +6421,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -6119,7 +6443,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -6141,7 +6465,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -6163,7 +6487,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -6183,47 +6507,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Ελληνικά), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Η σφαίρα τοποθετήθηκε σε έναν παράξενο [color:65845]θρόνο[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Ποιο είναι το αγαπημένο σας βιντεοπαιχνίδι, πείτε μας γιατί;</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 λέξεις</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6231,7 +6591,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6243,7 +6603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" style="9" min="1" max="1"/>
@@ -6453,96 +6813,92 @@
       <c r="E9" s="6" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="9">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>timer.sectionExpiredAlert</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Global (timer)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Alert()</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Section {s} time has expired. Your responses have been saved and you will now proceed to the next section.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1" s="9">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>noscript / JS disabled</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="9">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>noscript.title</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>noscript</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Heading</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>JavaScript Required</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1" s="9">
       <c r="A12" s="11" t="inlineStr">
         <is>
+          <t>noscript.title</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>noscript</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>JavaScript Required</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="9">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
           <t>noscript.body</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>noscript</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Paragraph</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Security compliance protocols require JavaScript execution to be active to view and complete this assessment.</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" s="9">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="E13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1" s="9">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Security hardlock screens</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>hardlock.multiTab.titleDefault</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Security - multi-tab hardlock</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Heading (HTML default value)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Access Restriction Engaged</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Overwritten in JS if a duplicate session is detected (see next row).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" s="9">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>hardlock.multiTab.bodyDefault</t>
+          <t>hardlock.multiTab.titleDefault</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -6552,20 +6908,24 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Paragraph (HTML default value)</t>
+          <t>Heading (HTML default value)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Active session tracking policy restricts this assessment to a single authorized tab view concurrently.</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
+          <t>Access Restriction Engaged</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Overwritten in JS if a duplicate session is detected (see next row).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="9">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>hardlock.duplicateSession.title</t>
+          <t>hardlock.multiTab.bodyDefault</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -6575,12 +6935,12 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Heading (set in JS)</t>
+          <t>Paragraph (HTML default value)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Duplicate Session Detected</t>
+          <t>Active session tracking policy restricts this assessment to a single authorized tab view concurrently.</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
@@ -6588,7 +6948,7 @@
     <row r="17" ht="28" customHeight="1" s="9">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>hardlock.duplicateSession.body</t>
+          <t>hardlock.duplicateSession.title</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -6598,12 +6958,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Paragraph (set in JS)</t>
+          <t>Heading (set in JS)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>An active assessment workflow for this email parameter is already running inside an independent tab window context.</t>
+          <t>Duplicate Session Detected</t>
         </is>
       </c>
       <c r="E17" s="6" t="n"/>
@@ -6611,22 +6971,22 @@
     <row r="18" ht="16" customHeight="1" s="9">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>hardlock.mobileBlock.title</t>
+          <t>hardlock.duplicateSession.body</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Security - mobile hardlock</t>
+          <t>Security - multi-tab hardlock</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Heading (set in JS)</t>
+          <t>Paragraph (set in JS)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Desktop Environment Required</t>
+          <t>An active assessment workflow for this email parameter is already running inside an independent tab window context.</t>
         </is>
       </c>
       <c r="E18" s="6" t="n"/>
@@ -6634,113 +6994,113 @@
     <row r="19" ht="42" customHeight="1" s="9">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>hardlock.mobileBlock.title</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Security - mobile hardlock</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Heading (set in JS)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Desktop Environment Required</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="9">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>hardlock.mobileBlock.body</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Security - mobile hardlock</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Paragraph (set in JS)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>For security compliance and layout integrity, this LQA assessment can only be completed on a desktop or laptop computer. Mobile viewports are restricted.</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" s="9">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1" s="9">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Focus-loss protection overlay</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="16" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>shield.title</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Anti-capture overlay (greyShield)</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Content Protected</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>shield.title</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Anti-capture overlay (greyShield)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Content Protected</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="9">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>shield.instructions</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Anti-capture overlay (greyShield)</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Bring your cursor back inside the window to reveal the test.</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="9">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1" s="9">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Global floating buttons</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="16" customHeight="1" s="9">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>button.resetQA</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Floating buttons</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>🛠️ Reset QA Session</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>confirm.resetQA</t>
+          <t>button.resetQA</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -6750,12 +7110,12 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>confirm() JS</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Are you sure you want to reset the QA Session? This will erase all state data.</t>
+          <t>🛠️ Reset QA Session</t>
         </is>
       </c>
       <c r="E25" s="6" t="n"/>
@@ -6763,7 +7123,7 @@
     <row r="26" ht="16" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>button.themeToggle.dark</t>
+          <t>confirm.resetQA</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -6773,12 +7133,12 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Button (light mode state)</t>
+          <t>confirm() JS</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>🌙 Dark Mode</t>
+          <t>Are you sure you want to reset the QA Session? This will erase all state data.</t>
         </is>
       </c>
       <c r="E26" s="6" t="n"/>
@@ -6786,60 +7146,60 @@
     <row r="27" ht="16" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>button.themeToggle.dark</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Floating buttons</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Button (light mode state)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>🌙 Dark Mode</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="9">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>button.themeToggle.light</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Floating buttons</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Button (dark mode state)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>☀️ Light Mode</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="E28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1" s="9">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Anti-cheat</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="16" customHeight="1" s="9">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>alert.printScreen</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Anti-cheat</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Alert()</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Action restricted for security compliance.</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>clipboard.screenshotBlockedText</t>
+          <t>alert.printScreen</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -6849,12 +7209,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Text injected into the clipboard</t>
+          <t>Alert()</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>[Screenshot restricted for security compliance]</t>
+          <t>Action restricted for security compliance.</t>
         </is>
       </c>
       <c r="E30" s="6" t="n"/>
@@ -6862,7 +7222,7 @@
     <row r="31" ht="16" customHeight="1" s="9">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>clipboard.copyBlockedText</t>
+          <t>clipboard.screenshotBlockedText</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -6877,7 +7237,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>[Copy restricted]</t>
+          <t>[Screenshot restricted for security compliance]</t>
         </is>
       </c>
       <c r="E31" s="6" t="n"/>
@@ -6885,60 +7245,60 @@
     <row r="32" ht="16" customHeight="1" s="9">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>clipboard.copyBlockedText</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Anti-cheat</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Text injected into the clipboard</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>[Copy restricted]</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="9">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>clipboard.pasteBlockedText</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Anti-cheat</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Replacement text in the field</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>[Paste restricted for security compliance]</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" s="9">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="E33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1" s="9">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Page 1 — Candidate registration</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="16" customHeight="1" s="9">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>page1.sectionTitle</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Section title</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Candidate Identity Registration</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1" s="9">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>page1.intro</t>
+          <t>page1.sectionTitle</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -6948,12 +7308,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Paragraph</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Please provide your identification credentials below. All fields are mandatory.</t>
+          <t>Candidate Identity Registration</t>
         </is>
       </c>
       <c r="E35" s="6" t="n"/>
@@ -6961,7 +7321,7 @@
     <row r="36" ht="42" customHeight="1" s="9">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>page1.tip</t>
+          <t>page1.intro</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -6971,12 +7331,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Inline alert</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TIP: You have two hours to complete the test. It will submit automatically after that delay. Read carefully and consult the provided documentation layout.</t>
+          <t>Please provide your identification credentials below. All fields are mandatory.</t>
         </is>
       </c>
       <c r="E36" s="6" t="n"/>
@@ -6984,7 +7344,7 @@
     <row r="37" ht="16" customHeight="1" s="9">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>page1.label.firstName</t>
+          <t>page1.tip</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -6994,12 +7354,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Inline alert</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>TIP: Each section has its own timer — Section A: 30 min, Section B: 45 min, Section C: 45 min. Read carefully and consult the provided documentation.</t>
         </is>
       </c>
       <c r="E37" s="6" t="n"/>
@@ -7007,7 +7367,7 @@
     <row r="38" ht="16" customHeight="1" s="9">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>page1.placeholder.firstName</t>
+          <t>page1.label.firstName</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -7017,12 +7377,12 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>e.g., John</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="E38" s="6" t="n"/>
@@ -7030,7 +7390,7 @@
     <row r="39" ht="16" customHeight="1" s="9">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>page1.label.lastName</t>
+          <t>page1.placeholder.firstName</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -7040,12 +7400,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Placeholder</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>e.g., John</t>
         </is>
       </c>
       <c r="E39" s="6" t="n"/>
@@ -7053,7 +7413,7 @@
     <row r="40" ht="16" customHeight="1" s="9">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>page1.placeholder.lastName</t>
+          <t>page1.label.lastName</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -7063,12 +7423,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>e.g., Doe</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="E40" s="6" t="n"/>
@@ -7076,7 +7436,7 @@
     <row r="41" ht="16" customHeight="1" s="9">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>page1.label.email</t>
+          <t>page1.placeholder.lastName</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -7086,12 +7446,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Placeholder</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>E-mail Address</t>
+          <t>e.g., Doe</t>
         </is>
       </c>
       <c r="E41" s="6" t="n"/>
@@ -7099,7 +7459,7 @@
     <row r="42" ht="16" customHeight="1" s="9">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>page1.placeholder.email</t>
+          <t>page1.label.email</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -7109,12 +7469,12 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>e.g., john.doe@example.com</t>
+          <t>E-mail Address</t>
         </is>
       </c>
       <c r="E42" s="6" t="n"/>
@@ -7122,7 +7482,7 @@
     <row r="43" ht="16" customHeight="1" s="9">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>page1.label.targetLanguage</t>
+          <t>page1.placeholder.email</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -7132,12 +7492,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Placeholder</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Assessment Target Language</t>
+          <t>e.g., john.doe@example.com</t>
         </is>
       </c>
       <c r="E43" s="6" t="n"/>
@@ -7145,7 +7505,7 @@
     <row r="44" ht="16" customHeight="1" s="9">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>page1.button.start</t>
+          <t>page1.label.targetLanguage</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -7155,12 +7515,12 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Start Test &amp; Proceed</t>
+          <t>Assessment Target Language</t>
         </is>
       </c>
       <c r="E44" s="6" t="n"/>
@@ -7168,7 +7528,7 @@
     <row r="45" ht="28" customHeight="1" s="9">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>page1.alert.missingFields</t>
+          <t>page1.button.start</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -7178,12 +7538,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Alert()</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>All identification parameters including Language selection are mandatory.</t>
+          <t>Start Test &amp; Proceed</t>
         </is>
       </c>
       <c r="E45" s="6" t="n"/>
@@ -7191,60 +7551,60 @@
     <row r="46" ht="56" customHeight="1" s="9">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>page1.alert.missingFields</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Alert()</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>All identification parameters including Language selection are mandatory.</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="9">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>page1.languageGrid.note</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Page 1 — Language grid</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Note (no text to translate here)</t>
         </is>
       </c>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Each language card's native name / region / flag is hardcoded directly in the HTML grid (not in the JS object). See each language tab's 'Language card metadata' section for the corresponding values to externalize.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" s="9">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="48" ht="16" customHeight="1" s="9">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Page 2 — Section A (Bugs)</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="16" customHeight="1" s="9">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>page2.sidebar.bugTypesTitle</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Page 2 — side panel</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>BUG TYPES:</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n"/>
     </row>
     <row r="49" ht="70" customHeight="1" s="9">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>page2.sidebar.bugTypesBody.moved</t>
+          <t>page2.sidebar.bugTypesTitle</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -7254,43 +7614,43 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Note (restructured, see BugType_Entry_xx rows below)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>DECISION (Priority 0, #7): the previous single truncated string ('Overlap... Wrong Language...') has been replaced by a proper, expandable, ID-based list — see the BugType_Entry_01 to BugType_Entry_10 rows right below. Add/remove/reorder rows as needed; the list is not capped at 10.</t>
-        </is>
-      </c>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>BUG TYPES:</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1" s="9">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_01</t>
+          <t>page2.sidebar.bugTypesBody.moved</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Page 2 — side panel (bug types list)</t>
+          <t>Page 2 — side panel</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>List entry</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Overlap — Text or UI elements visually overlapping.</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="n"/>
+          <t>Note (restructured, see BugType_Entry_xx rows below)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (Priority 0, #7): the previous single truncated string ('Overlap... Wrong Language...') has been replaced by a proper, expandable, ID-based list — see the BugType_Entry_01 to BugType_Entry_10 rows right below. Add/remove/reorder rows as needed; the list is not capped at 10.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="9">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_02</t>
+          <t>BugType_Entry_01</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -7305,7 +7665,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Truncation — Text cut off or clipped due to insufficient space.</t>
+          <t>Overlap — Text or UI elements visually overlapping.</t>
         </is>
       </c>
       <c r="E51" s="6" t="n"/>
@@ -7313,7 +7673,7 @@
     <row r="52" ht="28" customHeight="1" s="9">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_03</t>
+          <t>BugType_Entry_02</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -7328,7 +7688,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Wrong Language — Text displayed in a language other than the target language.</t>
+          <t>Truncation — Text cut off or clipped due to insufficient space.</t>
         </is>
       </c>
       <c r="E52" s="6" t="n"/>
@@ -7336,7 +7696,7 @@
     <row r="53" ht="16" customHeight="1" s="9">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_04</t>
+          <t>BugType_Entry_03</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -7351,7 +7711,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Untranslated Text — Source (English) text left untranslated.</t>
+          <t>Wrong Language — Text displayed in a language other than the target language.</t>
         </is>
       </c>
       <c r="E53" s="6" t="n"/>
@@ -7359,7 +7719,7 @@
     <row r="54" ht="28" customHeight="1" s="9">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_05</t>
+          <t>BugType_Entry_04</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -7374,7 +7734,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Mistranslation — Translated text does not match the intended meaning of the source.</t>
+          <t>Untranslated Text — Source (English) text left untranslated.</t>
         </is>
       </c>
       <c r="E54" s="6" t="n"/>
@@ -7382,7 +7742,7 @@
     <row r="55" ht="28" customHeight="1" s="9">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_06</t>
+          <t>BugType_Entry_05</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -7397,7 +7757,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent Terminology — The same source term translated differently across the build.</t>
+          <t>Mistranslation — Translated text does not match the intended meaning of the source.</t>
         </is>
       </c>
       <c r="E55" s="6" t="n"/>
@@ -7405,7 +7765,7 @@
     <row r="56" ht="28" customHeight="1" s="9">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_07</t>
+          <t>BugType_Entry_06</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -7420,7 +7780,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Grammar / Spelling Error — Grammatical or orthographic mistakes in the target text.</t>
+          <t>Inconsistent Terminology — The same source term translated differently across the build.</t>
         </is>
       </c>
       <c r="E56" s="6" t="n"/>
@@ -7428,7 +7788,7 @@
     <row r="57" ht="28" customHeight="1" s="9">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_08</t>
+          <t>BugType_Entry_07</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -7443,7 +7803,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Placeholder / Variable Error — Broken, missing, or mismatched placeholders/variables (e.g. {0}, [KIT], %s).</t>
+          <t>Grammar / Spelling Error — Grammatical or orthographic mistakes in the target text.</t>
         </is>
       </c>
       <c r="E57" s="6" t="n"/>
@@ -7451,7 +7811,7 @@
     <row r="58" ht="28" customHeight="1" s="9">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_09</t>
+          <t>BugType_Entry_08</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -7466,7 +7826,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Formatting / Line Break Issue — Incorrect line breaks, spacing, or text formatting.</t>
+          <t>Placeholder / Variable Error — Broken, missing, or mismatched placeholders/variables (e.g. {0}, [KIT], %s).</t>
         </is>
       </c>
       <c r="E58" s="6" t="n"/>
@@ -7474,7 +7834,7 @@
     <row r="59" ht="42" customHeight="1" s="9">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>BugType_Entry_10</t>
+          <t>BugType_Entry_09</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -7489,42 +7849,42 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Context Mismatch — Translation is technically correct but inappropriate for the in-game context.</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>PROPOSED completion of the previously truncated list — please review/adjust this taxonomy before publishing; it was authored as a standard LQA bug-type list, not pulled from an existing internal reference.</t>
-        </is>
-      </c>
+          <t>Formatting / Line Break Issue — Incorrect line breaks, spacing, or text formatting.</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1" s="9">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>page2.sidebar.reportTitle</t>
+          <t>BugType_Entry_10</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Page 2 — side panel</t>
+          <t>Page 2 — side panel (bug types list)</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>List entry</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>How to report a Bug:</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="n"/>
+          <t>Context Mismatch — Translation is technically correct but inappropriate for the in-game context.</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>PROPOSED completion of the previously truncated list — please review/adjust this taxonomy before publishing; it was authored as a standard LQA bug-type list, not pulled from an existing internal reference.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="28" customHeight="1" s="9">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>page2.sidebar.reportTemplate</t>
+          <t>page2.sidebar.reportTitle</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -7534,47 +7894,47 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Multi-line text</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Summary\nStep to repro:\n1.\n2.\nObserved behavior\nExpected behavior</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Use a literal \n to mark a line break inside this cell; the build step turns each literal \n into a real newline character.</t>
-        </is>
-      </c>
+          <t>How to report a Bug:</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1" s="9">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>page2.sectionTitle</t>
+          <t>page2.sidebar.reportTemplate</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Page 2</t>
+          <t>Page 2 — side panel</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Section title</t>
+          <t>Multi-line text</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Section A: LQA Bugs</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="n"/>
+          <t>Summary\nStep to repro:\n1.\n2.\nObserved behavior\nExpected behavior</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Use a literal \n to mark a line break inside this cell; the build step turns each literal \n into a real newline character.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="28" customHeight="1" s="9">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>page2.intro</t>
+          <t>page2.sectionTitle</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -7584,12 +7944,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Paragraph</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Identify structural or translation bugs from the provided gaming screenshots.</t>
+          <t>Section A: LQA Bugs</t>
         </is>
       </c>
       <c r="E63" s="6" t="n"/>
@@ -7597,7 +7957,7 @@
     <row r="64" ht="28" customHeight="1" s="9">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>page2.q1</t>
+          <t>page2.intro</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -7607,12 +7967,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q1)</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>1. Context: The game is Cat-Fu, the devs are from Japan and you are testing in English. Find the issue.</t>
+          <t>Identify structural or translation bugs from the provided gaming screenshots.</t>
         </is>
       </c>
       <c r="E64" s="6" t="n"/>
@@ -7620,7 +7980,7 @@
     <row r="65" ht="28" customHeight="1" s="9">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>page2.q2</t>
+          <t>page2.q1-example</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -7630,12 +7990,12 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q2)</t>
+          <t>Question label (lbl_q1)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>2. Context: The game is LQA Tycoon, the devs are from the United States of America and you are testing in Latin.</t>
+          <t>Here is an example to follow. Remember to check the guide on the left and to read the context carefully. Context: The game is Pawns of Fire vs Dark Claws, you are playing in English. Mode: Multiplayer, offline, Mega Death Fight. You just defeated your opponent with a Puuuurfect.</t>
         </is>
       </c>
       <c r="E65" s="6" t="n"/>
@@ -7643,7 +8003,7 @@
     <row r="66" ht="84" customHeight="1" s="9">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>page2.q3</t>
+          <t>page2.q1-2</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -7653,24 +8013,20 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q3)</t>
+          <t>Question label (lbl_q2)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>3. Diagnostic Node 3.</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>⚠ NEEDS CONTENT — DECISION (Priority 0, #7) was to fix this placeholder since it is not part of the intentional exercise design, but I do not have access to the actual image at screenshots/screenshot3.jpg, so I cannot author an accurate context/bug description for it. Left unchanged on purpose rather than inventing a fictional scenario — please supply the real context text for this question.</t>
-        </is>
-      </c>
+          <t>1-2. Context: The game is Neon Racers, developed by a Brazilian studio, testing in English. A UI element appears corrupted after finishing a race in split-screen mode.</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n"/>
     </row>
     <row r="67" ht="28" customHeight="1" s="9">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>page2.q4</t>
+          <t>page2.q1-3</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -7680,85 +8036,85 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q4)</t>
+          <t>Question label (lbl_q3)</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>4. Diagnostic Node 4.</t>
+          <t>1-3. Diagnostic Node 3.</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>⚠ Same situation as Q3 — see note above (screenshots/screenshot4.jpg not available to me).</t>
+          <t>⚠ NEEDS CONTENT — DECISION (Priority 0, #7) was to fix this placeholder since it is not part of the intentional exercise design, but I do not have access to the actual image at screenshots/screenshot3.jpg, so I cannot author an accurate context/bug description for it. Left unchanged on purpose rather than inventing a fictional scenario — please supply the real context text for this question.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="9">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>page2.imageEnlargeHint</t>
+          <t>page2.q1-4</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Page 2 + Lightbox (reused for Q1-Q4)</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Hint text</t>
+          <t>Question label (lbl_q4)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>🔍 Click to enlarge</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n"/>
+          <t>1-4. Context: The game is Stellar Forge, developed by a Korean studio, testing in English. A string appears untranslated on the crafting menu after equipping a legendary item.</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Same situation as Q3 — see note above (screenshots/screenshot4.jpg not available to me).</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="9">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>page2.altText.q1</t>
+          <t>page2.q1-5</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Page 2 — accessibility</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Image alt</t>
-        </is>
-      </c>
+          <t>Page 2</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n"/>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Bug Cat-Fu</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n"/>
+          <t>1-5. Context: The game is CrimeCity Vice, developed by a French studio, testing in English. An in-game notification overlaps the HUD during a cutscene transition.</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1" s="9">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>page2.altText.q2</t>
+          <t>page2.imageEnlargeHint</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Page 2 — accessibility</t>
+          <t>Page 2 + Lightbox (reused for Q1-Q4)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Image alt</t>
+          <t>Hint text</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Bug LQA Tycoon</t>
+          <t>🔍 Click to enlarge</t>
         </is>
       </c>
       <c r="E70" s="6" t="n"/>
@@ -7766,7 +8122,7 @@
     <row r="71" ht="16" customHeight="1" s="9">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>page2.altText.q3</t>
+          <t>page2.altText.q1-example</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -7781,19 +8137,15 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>Same as Q4 — not very descriptive, could be improved if possible.</t>
-        </is>
-      </c>
+          <t>Bug Cat-Fu</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1" s="9">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>page2.altText.q4</t>
+          <t>page2.altText.q1-2</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -7808,24 +8160,20 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>Same as Q3 — not very descriptive, could be improved if possible.</t>
-        </is>
-      </c>
+          <t>Screenshot Neon Racers</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1" s="9">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>lightbox.altText</t>
+          <t>page2.altText.q1-3</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Fullscreen lightbox (all pages with an image)</t>
+          <t>Page 2 — accessibility</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -7835,168 +8183,172 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Fullscreen Asset View</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="n"/>
+          <t>Screenshot 3</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Same as Q4 — not very descriptive, could be improved if possible.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="9">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>page2.button.next</t>
+          <t>page2.altText.q1-4</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Page 2</t>
+          <t>Page 2 — accessibility</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Image alt</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Next Section →</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="n"/>
+          <t>Screenshot Stellar Forge</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Same as Q3 — not very descriptive, could be improved if possible.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="9">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>Page 3 — Section B (Translation)</t>
-        </is>
-      </c>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>page2.altText.q1-5</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Page 2 — accessibility</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Screenshot CrimeCity Vice</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n"/>
     </row>
     <row r="76" ht="98" customHeight="1" s="9">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>page3.sidebar.glossaryTitle</t>
+          <t>lightbox.altText</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Page 3 — side panel</t>
+          <t>Fullscreen lightbox (all pages with an image)</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Image alt</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>GLOSSARY</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>DECISION (Priority 0, #5): stays in English for every language, no per-language translation. The previous two separate header cells (an 'EN' source-column header and a per-language target-column header) are now merged into a single header spanning both columns, since the column header is no longer translated either — see page3.glossary.mergedHeader below. The per-language 'glossary header' field has been removed from every language tab.</t>
-        </is>
-      </c>
+          <t>Fullscreen Asset View</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n"/>
     </row>
     <row r="77" ht="28" customHeight="1" s="9">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>page3.glossary.mergedHeader</t>
+          <t>page2.button.next</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Page 3 — glossary table</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Merged column header (spans both EN + target columns)</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>GLOSSARY</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>Replaces the previous pair of separate headers ('EN' + a per-language translated word). Always English, per the decision above.</t>
-        </is>
-      </c>
+          <t>Submit Section →</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n"/>
     </row>
     <row r="78" ht="16" customHeight="1" s="9">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>page3.sectionTitle</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Section title</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Section B: Proofreading/Translation</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="n"/>
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Page 3 — Section B (Translation)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="28" customHeight="1" s="9">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>page3.intro</t>
+          <t>page3.sidebar.glossaryTitle</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Page 3</t>
+          <t>Page 3 — side panel</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Paragraph</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Review and track translation accuracy with the help of the local documentation matrix.</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="n"/>
+          <t>GLOSSARY</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (Priority 0, #5): stays in English for every language, no per-language translation. The previous two separate header cells (an 'EN' source-column header and a per-language target-column header) are now merged into a single header spanning both columns, since the column header is no longer translated either — see page3.glossary.mergedHeader below. The per-language 'glossary header' field has been removed from every language tab.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="84" customHeight="1" s="9">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>page3.referenceText.moved</t>
+          <t>page3.glossary.mergedHeader</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Page 3</t>
+          <t>Page 3 — glossary table</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Note (moved, no duplicate here)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="n"/>
+          <t>Merged column header (spans both EN + target columns)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>The English SOURCE text shown in the LEFT column of the Q5/Q6/Q7 proofreading tables is not listed here: it lives in each language tab (section 'Proofreading'), right next to its own translated target text. Goal: allow a different proofreading scenario per language (and, eventually, per question) without duplicating a 'shared' text across 32 places that was never meant to stay identical forever.</t>
+          <t>Replaces the previous pair of separate headers ('EN' + a per-language translated word). Always English, per the decision above.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="9">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>page3.q5</t>
+          <t>page3.sectionTitle</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -8006,12 +8358,12 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q5)</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>5. Proofread Segment Alpha.</t>
+          <t>Section B: Proofreading/Translation</t>
         </is>
       </c>
       <c r="E81" s="6" t="n"/>
@@ -8019,7 +8371,7 @@
     <row r="82" ht="16" customHeight="1" s="9">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>page3.q6</t>
+          <t>page3.intro</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -8029,12 +8381,12 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q6)</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>6. Proofread Segment Beta.</t>
+          <t>Review and track translation accuracy with the help of the local documentation matrix.</t>
         </is>
       </c>
       <c r="E82" s="6" t="n"/>
@@ -8042,7 +8394,7 @@
     <row r="83" ht="16" customHeight="1" s="9">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>page3.q7</t>
+          <t>page3.referenceText.moved</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -8052,20 +8404,20 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Question label (lbl_q7)</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>7. Proofread Segment Gamma.</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="n"/>
+          <t>Note (moved, no duplicate here)</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>The English SOURCE text shown in the LEFT column of the Q5/Q6/Q7 proofreading tables is not listed here: it lives in each language tab (section 'Proofreading'), right next to its own translated target text. Goal: allow a different proofreading scenario per language (and, eventually, per question) without duplicating a 'shared' text across 32 places that was never meant to stay identical forever.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="9">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>page3.button.previous</t>
+          <t>page3.q2-1</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -8075,12 +8427,12 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Question label (lbl_q5)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>← Previous Section</t>
+          <t>2-1. Proofread Segment Alpha.</t>
         </is>
       </c>
       <c r="E84" s="6" t="n"/>
@@ -8088,7 +8440,7 @@
     <row r="85" ht="16" customHeight="1" s="9">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>page3.button.next</t>
+          <t>page3.q2-2</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -8098,42 +8450,54 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Question label (lbl_q6)</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Next Section →</t>
+          <t>2-2. Proofread Segment Beta.</t>
         </is>
       </c>
       <c r="E85" s="6" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1" s="9">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Page 4 — Section C (Writing)</t>
-        </is>
-      </c>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>page3.q2-3</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Question label (lbl_q7)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>2-3. Proofread Segment Gamma.</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n"/>
     </row>
     <row r="87" ht="16" customHeight="1" s="9">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>page4.sectionTitle</t>
+          <t>page3.q2-4</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Page 4</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Section title</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n"/>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Section C: Writing Skill</t>
+          <t>2-4. Proofread Segment Delta.</t>
         </is>
       </c>
       <c r="E87" s="6" t="n"/>
@@ -8141,22 +8505,18 @@
     <row r="88" ht="28" customHeight="1" s="9">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>page4.intro</t>
+          <t>page3.q2-5</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Page 4</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Paragraph</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n"/>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Assess and record writing patterns. Answer utilizing the language specified in the question prompts.</t>
+          <t>2-5. Translate the following PlayStation 5 system error message into the target language. Respect Sony's localization compliance guidelines (no truncation, maintain formal register, preserve error code format).</t>
         </is>
       </c>
       <c r="E88" s="6" t="n"/>
@@ -8164,76 +8524,56 @@
     <row r="89" ht="42" customHeight="1" s="9">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>page4.q8</t>
+          <t>page3.q2-5.source</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Page 4</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Question label (lbl_q8)</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n"/>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>8. What was the last game you enjoyed the most recently? Try to tell us why (150 words).</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>DECISION (Priority 0, #2): confirmed intentional. Q8 is a deliberate English-only writing exercise and stays in English for every candidate regardless of target language — no change made.</t>
-        </is>
-      </c>
+          <t>An error has occurred (CE-108255-1). The game data may be corrupted. Please delete the application and reinstall it from your library. If the issue persists, visit PlayStation Support.</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n"/>
     </row>
     <row r="90" ht="42" customHeight="1" s="9">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>page4.q9.cjkSuffix</t>
+          <t>page3.q2-6</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Page 4 — suffix generated in JS for zh / ja / ko / th</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>JS-generated text (always English)</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n"/>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>(Equivalent of 250 English words (dynamically calculated based on character density))</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>DECISION (Priority 0, #3): confirmed intentional. This suffix stays hardcoded in English for zh/ja/ko/th candidates by design — no change made.</t>
-        </is>
-      </c>
+          <t>2-6. Translate the following Nintendo eShop connection message into the target language. Follow Nintendo's localization standards (natural phrasing, family-friendly tone, no literal translation of UI button names).</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n"/>
     </row>
     <row r="91" ht="16" customHeight="1" s="9">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>page4.button.previous</t>
+          <t>page3.q2-6.source</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Page 4</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n"/>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>← Previous Section</t>
+          <t>Unable to connect to Nintendo eShop. Please check your internet connection settings or try again later. Visit support.nintendo.com for assistance. Error Code: 2811-5001.</t>
         </is>
       </c>
       <c r="E91" s="6" t="n"/>
@@ -8241,52 +8581,56 @@
     <row r="92" ht="16" customHeight="1" s="9">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>page4.button.submit</t>
+          <t>page3.q2-7</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Page 4</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n"/>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Finish &amp; Submit Test</t>
+          <t>2-7. Translate the following Xbox system prompt into the target language. Apply Microsoft's localization guidelines (consistent controller button naming per Xbox Terminology, active voice, concise phrasing).</t>
         </is>
       </c>
       <c r="E92" s="6" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1" s="9">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>Submission confirmation modal</t>
-        </is>
-      </c>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>page3.q2-7.source</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Your controller has been disconnected. Please reconnect your controller and press the A Button to continue. Check the battery level if the issue persists. Error: 0x82D40003.</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n"/>
     </row>
     <row r="94" ht="16" customHeight="1" s="9">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>modal.title</t>
+          <t>page3.q2-8</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Modal</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Heading (h3)</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n"/>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Submit Assessment</t>
+          <t>2-8. Translate the following sports commentary excerpt into the target language. Preserve the energy and technical terminology of US basketball broadcasting. Variables in {curly braces} must not be translated.</t>
         </is>
       </c>
       <c r="E94" s="6" t="n"/>
@@ -8294,22 +8638,18 @@
     <row r="95" ht="16" customHeight="1" s="9">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>modal.text.default</t>
+          <t>page3.q2-8.source</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Modal</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Paragraph (default, all questions answered)</t>
-        </is>
-      </c>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n"/>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>You are about to transmit your completed test file. Continue?</t>
+          <t>{player_name} rises up from the top of the key, hangs in the air for a split second, and throws down a thunderous two-handed slam â€” and the {team_name} crowd goes absolutely wild!</t>
         </is>
       </c>
       <c r="E95" s="6" t="n"/>
@@ -8317,22 +8657,22 @@
     <row r="96" ht="16" customHeight="1" s="9">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>modal.text.warningPrefix</t>
+          <t>page3.button.previous</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Page 3</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Paragraph (JS-generated, missing answers)</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>WARNING: You have not answered all questions!</t>
+          <t>← Previous Section</t>
         </is>
       </c>
       <c r="E96" s="6" t="n"/>
@@ -8340,72 +8680,52 @@
     <row r="97" ht="16" customHeight="1" s="9">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>modal.text.warningFieldsIntro</t>
+          <t>page3.button.next</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Page 3</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Paragraph (JS-generated, missing answers)</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>The following input fields are still empty:</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>Followed by the dynamically generated 'Q1, Q3, ...' list.</t>
-        </is>
-      </c>
+          <t>Submit Section →</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n"/>
     </row>
     <row r="98" ht="16" customHeight="1" s="9">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>modal.text.warningConfirm</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Modal</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Paragraph (JS-generated, missing answers)</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>Are you sure you want to proceed and finalize transmission?</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="n"/>
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Page 4 — Section C (Writing)</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="9">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>modal.button.yes</t>
+          <t>page4.sectionTitle</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Yes, Send</t>
+          <t>Section C: Writing Skill</t>
         </is>
       </c>
       <c r="E99" s="6" t="n"/>
@@ -8413,75 +8733,99 @@
     <row r="100" ht="16" customHeight="1" s="9">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>modal.button.no</t>
+          <t>page4.intro</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>No, Back</t>
+          <t>Assess and record writing patterns. Answer utilizing the language specified in the question prompts.</t>
         </is>
       </c>
       <c r="E100" s="6" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="9">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>Page 5 — Results / Summary</t>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>page4.q3-1</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Page 4</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Question label (lbl_q8)</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>8. What was the last game you enjoyed the most recently? Try to tell us why (150 words).</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (Priority 0, #2): confirmed intentional. Q8 is a deliberate English-only writing exercise and stays in English for every candidate regardless of target language — no change made.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="9">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>page5.thanksTitle</t>
+          <t>page4.q3-2.cjkSuffix</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 4 — suffix generated in JS for zh / ja / ko / th</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Heading (h2)</t>
+          <t>JS-generated text (always English)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Thank you for taking part in our test.</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="n"/>
+          <t>(Equivalent of 250 English words (dynamically calculated based on character density))</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (Priority 0, #3): confirmed intentional. This suffix stays hardcoded in English for zh/ja/ko/th candidates by design — no change made.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="28" customHeight="1" s="9">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>page5.thanksBody</t>
+          <t>page4.button.previous</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Paragraph</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>We will contact you shortly. Your compiled assessment logs are rendered below.</t>
+          <t>← Previous Section</t>
         </is>
       </c>
       <c r="E103" s="6" t="n"/>
@@ -8489,72 +8833,52 @@
     <row r="104" ht="16" customHeight="1" s="9">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>page5.languageBoxPrefix</t>
+          <t>page4.button.submit</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>JS-generated text</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Language: </t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>Followed by the selected language code (e.g. 'fr-FR').</t>
-        </is>
-      </c>
+          <t>Finish &amp; Submit Test</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="n"/>
     </row>
     <row r="105" ht="16" customHeight="1" s="9">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>page5.button.downloadPdf</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>Page 5</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>Download My Responses (PDF)</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="n"/>
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Submission confirmation modal</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="9">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>page5.sectionTitle</t>
+          <t>modal.title</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Section title</t>
+          <t>Heading (h3)</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Your Submitted Responses</t>
+          <t>Submit Assessment</t>
         </is>
       </c>
       <c r="E106" s="6" t="n"/>
@@ -8562,79 +8886,95 @@
     <row r="107" ht="28" customHeight="1" s="9">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>page5.responseLabelPrefix</t>
+          <t>modal.text.default</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>JS-generated label (per response)</t>
+          <t>Paragraph (default, all questions answered)</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Response </t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>Followed by the question number (1 to 9). The question text itself is intentionally no longer shown here (earlier XSS fix).</t>
-        </is>
-      </c>
+          <t>You are about to transmit your completed test file. Continue?</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="9">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>Page 5 — Anonymous feedback block</t>
-        </is>
-      </c>
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>modal.text.warningPrefix</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Paragraph (JS-generated, missing answers)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>WARNING: You have not answered all questions!</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="n"/>
     </row>
     <row r="109" ht="16" customHeight="1" s="9">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>feedback.title</t>
+          <t>modal.text.warningFieldsIntro</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Heading (h3)</t>
+          <t>Paragraph (JS-generated, missing answers)</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Help us improve this assessment</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="n"/>
+          <t xml:space="preserve">The following input fields are still empty: </t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>Followed by the dynamically generated 'Q1, Q3, ...' list.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="28" customHeight="1" s="9">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>feedback.intro</t>
+          <t>modal.text.warningConfirm</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Paragraph</t>
+          <t>Paragraph (JS-generated, missing answers)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Please share your experience. This form is completely anonymous and detached from your candidate files.</t>
+          <t>Are you sure you want to proceed and finalize transmission?</t>
         </is>
       </c>
       <c r="E110" s="6" t="n"/>
@@ -8642,22 +8982,18 @@
     <row r="111" ht="16" customHeight="1" s="9">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>feedback.option.time</t>
+          <t>modal.sectionDefaultText</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Checkbox label</t>
-        </is>
-      </c>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Not enough time</t>
+          <t>You are about to validate and submit this section. Continue?</t>
         </is>
       </c>
       <c r="E111" s="6" t="n"/>
@@ -8665,22 +9001,18 @@
     <row r="112" ht="16" customHeight="1" s="9">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>feedback.option.bug</t>
+          <t>modal.sectionWarningPrefix</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Checkbox label</t>
-        </is>
-      </c>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="n"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Functional issue</t>
+          <t>WARNING: Some questions in this section are unanswered!</t>
         </is>
       </c>
       <c r="E112" s="6" t="n"/>
@@ -8688,22 +9020,18 @@
     <row r="113" ht="16" customHeight="1" s="9">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>feedback.option.unclear</t>
+          <t>modal.sectionWarningConfirm</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>Checkbox label</t>
-        </is>
-      </c>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n"/>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Unclear instructions</t>
+          <t>Are you sure you want to validate and submit this section anyway?</t>
         </is>
       </c>
       <c r="E113" s="6" t="n"/>
@@ -8711,22 +9039,22 @@
     <row r="114" ht="16" customHeight="1" s="9">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>feedback.option.other</t>
+          <t>modal.button.yes</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Checkbox label</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Other problem</t>
+          <t>Yes, Send</t>
         </is>
       </c>
       <c r="E114" s="6" t="n"/>
@@ -8734,68 +9062,52 @@
     <row r="115" ht="16" customHeight="1" s="9">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>feedback.placeholder</t>
+          <t>modal.button.no</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Share your detailed thoughts (optional)...</t>
+          <t>No, Back</t>
         </is>
       </c>
       <c r="E115" s="6" t="n"/>
     </row>
     <row r="116" ht="16" customHeight="1" s="9">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>feedback.button.submit</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>Page 5 — feedback</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>Submit Feedback</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="n"/>
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>Page 5 — Results / Summary</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="9">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>feedback.successMessage</t>
+          <t>page5.thanksTitle</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Confirmation text</t>
+          <t>Heading (h2)</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Thank you so much for your feedback!</t>
+          <t>Thank you for taking part in our test.</t>
         </is>
       </c>
       <c r="E117" s="6" t="n"/>
@@ -8803,22 +9115,22 @@
     <row r="118" ht="28" customHeight="1" s="9">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>feedback.alert.empty</t>
+          <t>page5.thanksBody</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Alert()</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Please select at least one issue checkbox or write a comment before submitting.</t>
+          <t>We will contact you shortly. Your compiled assessment logs are rendered below.</t>
         </is>
       </c>
       <c r="E118" s="6" t="n"/>
@@ -8826,52 +9138,72 @@
     <row r="119" ht="28" customHeight="1" s="9">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>feedback.alert.sendError</t>
+          <t>page5.languageBoxPrefix</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — feedback</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Alert()</t>
+          <t>JS-generated text</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Your feedback could not be sent (network or server issue). Please try submitting again.</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="n"/>
+          <t xml:space="preserve">Language: </t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Followed by the selected language code (e.g. 'fr-FR').</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1" s="9">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>Page 5 — Submission error banner</t>
-        </is>
-      </c>
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>page5.button.downloadPdf</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Page 5</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Download My Responses (PDF)</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="n"/>
     </row>
     <row r="121" ht="28" customHeight="1" s="9">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>submission.error.message</t>
+          <t>page5.sectionTitle</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — error banner</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>JS-generated text</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Submission failed (network or server issue). Your responses are still shown below — please retry, or download them locally in the meantime.</t>
+          <t>Your Submitted Responses</t>
         </is>
       </c>
       <c r="E121" s="6" t="n"/>
@@ -8879,75 +9211,79 @@
     <row r="122" ht="16" customHeight="1" s="9">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>submission.error.retryButton</t>
+          <t>page5.responseLabelPrefix</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Page 5 — error banner</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>JS-generated button</t>
+          <t>JS-generated label (per response)</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Retry submission</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="n"/>
+          <t xml:space="preserve">Response </t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Followed by the question number (1 to 9). The question text itself is intentionally no longer shown here (earlier XSS fix).</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="16" customHeight="1" s="9">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>submission.error.downloadButton</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>Page 5 — error banner</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>JS-generated button</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Download my responses</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="n"/>
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Page 5 — Anonymous feedback block</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="9">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>Internal payload sent to the Teams webhook (not shown to the candidate)</t>
-        </is>
-      </c>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>feedback.title</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Heading (h3)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Help us improve this assessment</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="n"/>
     </row>
     <row r="125" ht="16" customHeight="1" s="9">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>payload.emailLabel</t>
+          <t>feedback.intro</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Internal — Teams payload</t>
+          <t>Page 5 — feedback</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Label (Markdown bold)</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Email:</t>
+          <t>Please share your experience. This form is completely anonymous and detached from your candidate files.</t>
         </is>
       </c>
       <c r="E125" s="6" t="n"/>
@@ -8955,22 +9291,22 @@
     <row r="126" ht="16" customHeight="1" s="9">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>payload.durationLabel</t>
+          <t>feedback.option.time</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Internal — Teams payload</t>
+          <t>Page 5 — feedback</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Label (Markdown bold) + suffix</t>
+          <t>Checkbox label</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Duration: ... minutes</t>
+          <t>Not enough time</t>
         </is>
       </c>
       <c r="E126" s="6" t="n"/>
@@ -8978,246 +9314,559 @@
     <row r="127" ht="16" customHeight="1" s="9">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>payload.timeoutWarning</t>
+          <t>feedback.option.bug</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Internal — Teams payload</t>
+          <t>Page 5 — feedback</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Banner text</t>
+          <t>Checkbox label</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>AUTOMATIC SUBMISSION - TIME EXPIRED</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>Surrounded by ⚠️ emoji in the code.</t>
-        </is>
-      </c>
+          <t>Functional issue</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="n"/>
     </row>
     <row r="128" ht="16" customHeight="1" s="9">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>feedback.option.unclear</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>Checkbox label</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Unclear instructions</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>feedback.option.other</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Checkbox label</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>Other problem</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>feedback.placeholder</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>Share your detailed thoughts (optional)...</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>feedback.button.submit</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>feedback.successMessage</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Confirmation text</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Thank you so much for your feedback!</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>feedback.alert.empty</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Alert()</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Please select at least one issue checkbox or write a comment before submitting.</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>feedback.alert.sendError</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — feedback</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Alert()</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Your feedback could not be sent (network or server issue). Please try submitting again.</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>Page 5 — Submission error banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>submission.error.message</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — error banner</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>JS-generated text</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>Submission failed (network or server issue). Your responses are still shown below — please retry, or download them locally in the meantime.</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>submission.error.retryButton</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — error banner</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>JS-generated button</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>Retry submission</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>submission.error.downloadButton</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Page 5 — error banner</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>JS-generated button</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>Download my responses</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Internal payload sent to the Teams webhook (not shown to the candidate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>payload.emailLabel</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Internal — Teams payload</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Label (Markdown bold)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Email:</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>payload.durationLabel</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Internal — Teams payload</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Label (Markdown bold) + suffix</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Duration: ... minutes</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>payload.timeoutWarning</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Internal — Teams payload</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>Banner text</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>AUTOMATIC SUBMISSION - TIME EXPIRED</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Surrounded by ⚠️ emoji in the code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
           <t>payload.wordCountSuffix</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Internal — Teams payload (Q8/Q9 only)</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t>Label (Markdown italics)</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>(Word count: ... units)</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Word count: {n}</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>payload.durationUnit</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Internal — Teams payload</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Unit label (appended after duration number)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>minutes</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>payload.feedbackTitle</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Internal — Teams payload (feedback section)</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Section heading</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Anonymous Assessment Feedback Log</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>payload.feedback.categoriesLabel</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Internal — Teams payload (feedback section)</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Identified Categories:</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>payload.feedback.noneSelected</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Internal — Teams payload (feedback section)</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Fallback text (no checkbox ticked)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>None selected</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>payload.feedback.commentsLabel</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Internal — Teams payload (feedback section)</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Detailed Candidate Commentary:</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>payload.feedback.noComments</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Internal — Teams payload (feedback section)</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Fallback text (no comment written)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>[No detailed comments provided]</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>payload.noResponseFallback</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Internal — Teams payload (all questions)</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Fallback text (blank answer)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>[Left Blank / No response provided]</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>download.candidateLabel</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Page 5 — PDF download</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Label prefix</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Candidate:</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>download.languageLabel</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Page 5 — PDF download</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Label prefix</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Language:</t>
         </is>
@@ -9225,22 +9874,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A29:E29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9252,7 +9901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -9605,7 +10254,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -9627,7 +10276,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -9649,7 +10298,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -9671,7 +10320,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -9693,7 +10342,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -9715,7 +10364,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -9735,47 +10384,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Türkçe), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Küre garip bir [color:65845]taht[/color] üzerine yerleştirildi.[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>En sevdiğiniz video oyunu hangisi, nedenini bize söyleyin?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 kelime</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9783,7 +10468,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9795,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -10166,7 +10851,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -10188,7 +10873,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -10210,7 +10895,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -10232,7 +10917,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -10254,7 +10939,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -10276,7 +10961,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -10296,55 +10981,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Українська), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Сфера була розміщена на дивному [color:65845]троні[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Яка ваша улюблена відеогра, розкажіть чому?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 слів</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10356,7 +11077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -10731,7 +11452,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -10753,7 +11474,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -10775,7 +11496,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -10797,7 +11518,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -10819,7 +11540,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -10841,7 +11562,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -10861,55 +11582,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Română), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Orbul a fost plasat pe un tron [color:65845]straniu[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Care este jocul tău video preferat, spune-ne de ce?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 de cuvinte</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10921,7 +11678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -11296,7 +12053,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -11318,7 +12075,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -11340,7 +12097,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -11362,7 +12119,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -11384,7 +12141,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -11406,7 +12163,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -11426,55 +12183,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Български), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Сферата беше поставена на странен [color:65845]трон[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Коя е любимата ви видеоигра, разкажете ни защо?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 думи</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11486,7 +12279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -11861,7 +12654,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -11883,7 +12676,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -11905,7 +12698,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -11927,7 +12720,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -11949,7 +12742,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -11971,7 +12764,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -11991,47 +12784,83 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (العربية), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]تم وضع الجرم السماوي على [color:65845]عرش[/color] غريب.[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="70" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ما هي لعبتك الإلكترونية المفضلة، وأخبرنا لماذا؟</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="70" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 كلمة</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>FIXED (Priority 0, #3 — not intentional): no 'volumeLabel' was previously defined for Arabic, and since 'ar' is not matched by the zh/ja/ko/th detection regex, the code silently fell back to the hardcoded English '250 words' suffix even for Arabic candidates. Added this dedicated Arabic label so the suffix now displays correctly.</t>
         </is>
@@ -12041,9 +12870,9 @@
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12055,7 +12884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -12442,7 +13271,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -12464,7 +13293,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -12486,7 +13315,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -12508,7 +13337,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -12530,7 +13359,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -12552,7 +13381,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -12572,55 +13401,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (हिन्दी), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]गोले को एक अजीब [color:65845]सिंहासन[/color] पर रखा गया था।[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>आपका पसंदीदा वीडियो गेम कौन सा है, हमें बताएं क्यों?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 शब्द</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12632,7 +13497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -12985,7 +13850,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -13007,7 +13872,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -13029,7 +13894,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -13051,7 +13916,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -13073,7 +13938,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -13095,7 +13960,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -13115,43 +13980,79 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (简体中文), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]宝珠被放置在一个奇妙的[color:65845]王座[/color]上。[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>你最喜欢的电子游戏是什么，告诉我们为什么？</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>No 'volumeLabel' needed here: the code detects 'zh' and always shows the hardcoded English suffix (see EN_Common.page4.q9.cjkSuffix) — confirmed intentional, see Priority 0 decision #3.</t>
         </is>
@@ -13163,7 +14064,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13175,7 +14076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -13528,7 +14429,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -13550,7 +14451,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -13572,7 +14473,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -13594,7 +14495,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -13616,7 +14517,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -13638,7 +14539,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -13658,43 +14559,79 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (繁體中文), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]寶珠被放置在一個奇妙的[color:65845]王座[/color]上。[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>你最喜歡的電子遊戲是什麼，告訴我們為什麼？</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Same as zh-CN: word-count suffix always shown in English by design.</t>
         </is>
@@ -13706,7 +14643,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13718,7 +14655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -14071,7 +15008,7 @@
     <row r="22" ht="56" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -14093,7 +15030,7 @@
     <row r="23" ht="56" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -14115,7 +15052,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -14137,7 +15074,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -14159,7 +15096,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -14181,7 +15118,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -14201,47 +15138,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (繁體中文), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]寶珠被放置喺一個奇妙嘅[color:65845]王座[/color]上面。[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>你最鍾意邊款電子遊戲，話畀我哋知點解？</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Cantonese phrasing, clearly distinct from zh-TW — consistent, no change needed.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Same as zh-CN: word-count suffix always shown in English by design.</t>
         </is>
@@ -14253,7 +15226,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14265,7 +15238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -14618,7 +15591,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -14640,7 +15613,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -14662,7 +15635,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -14684,7 +15657,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -14706,7 +15679,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -14728,7 +15701,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -14748,43 +15721,79 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (日本語), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]宝珠は奇妙な[color:65845]玉座[/color]に置かれた。[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>あなたの好きなビデオゲームは何ですか、その理由を教えてください。</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Same as zh-CN: word-count suffix always shown in English by design.</t>
         </is>
@@ -14796,7 +15805,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14808,7 +15817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -15161,7 +16170,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -15183,7 +16192,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -15205,7 +16214,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -15227,7 +16236,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -15249,7 +16258,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -15271,7 +16280,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -15291,51 +16300,87 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="84" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Français), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]l'orbe était placée un trones[color:66845]étrange [/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Quel est ton jeu vidéo préféré, dis-nous pourquoi ?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>HARMONIZED (Priority 0, #6): replaced the previous unique proverb/Yoda-reference prompt with the standard 'favorite video game' question used by every other language, so all 32 languages now run the same Q9 exercise. Previous value (kept here for history only, not used anymore): "Tant va la cruche à l'eau qu'à la fin elle se pourfasse. Pensez-vous que Maître Yoda aurait apprécié un tel language ?"</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 mots</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -15343,7 +16388,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15355,7 +16400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -15708,7 +16753,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -15730,7 +16775,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -15752,7 +16797,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -15774,7 +16819,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -15796,7 +16841,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -15818,7 +16863,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -15838,43 +16883,79 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (한국어), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]오브가 기묘한[color:65845]왕좌[/color]에 놓였다.[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>가장 좋아하는 비디오 게임은 무엇인가요, 그 이유를 말해주세요.</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Same as zh-CN: word-count suffix always shown in English by design.</t>
         </is>
@@ -15886,7 +16967,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15898,7 +16979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -16251,7 +17332,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -16273,7 +17354,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -16295,7 +17376,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -16317,7 +17398,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -16339,7 +17420,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -16361,7 +17442,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -16381,47 +17462,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Tiếng Việt), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Quả cầu được đặt trên một ngai vàng [color:65845]kỳ lạ[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Trò chơi điện tử yêu thích của bạn là gì, hãy cho chúng tôi biết tại sao?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 từ</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -16429,7 +17546,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16441,7 +17558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -16794,7 +17911,7 @@
     <row r="22" ht="112" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -16816,7 +17933,7 @@
     <row r="23" ht="112" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -16838,7 +17955,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -16860,7 +17977,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -16882,7 +17999,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -16904,7 +18021,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -16924,43 +18041,79 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (ไทย), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]ลูกแก้วถูกวางไว้บนบัลลังก์[color:65845]ที่แปลกประหลาด[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>เกมโปรดของคุณคือเกมอะไร และบอกเหตุผลให้เราฟังหน่อย?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>No 'volumeLabel' needed here: the code detects 'th' and always shows the hardcoded English suffix (see EN_Common.page4.q9.cjkSuffix) — confirmed intentional, see Priority 0 decision #3.</t>
         </is>
@@ -16972,7 +18125,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16984,7 +18137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -17337,7 +18490,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -17359,7 +18512,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -17381,7 +18534,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -17403,7 +18556,7 @@
     <row r="25" ht="42" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -17425,7 +18578,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -17447,7 +18600,7 @@
     <row r="27" ht="42" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -17467,47 +18620,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Bahasa Melayu), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Sfera itu diletakkan di atas takhta yang [color:65845]aneh[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Apakah permainan video kegemaran anda, beritahu kami mengapa?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 patah perkataan</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -17515,7 +18704,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17527,7 +18716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -17902,7 +19091,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -17924,7 +19113,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -17946,7 +19135,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -17968,7 +19157,7 @@
     <row r="26" ht="42" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -17990,7 +19179,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -18012,7 +19201,7 @@
     <row r="28" ht="42" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -18032,55 +19221,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Bahasa Indonesia), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Orb ditempatkan di atas takhta yang [color:65845]aneh[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Apakah permainan video favorit Anda, beritahu kami mengapa?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 kata</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18092,7 +19317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -18445,7 +19670,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -18467,7 +19692,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -18489,7 +19714,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -18511,7 +19736,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -18533,7 +19758,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -18555,7 +19780,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -18575,47 +19800,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Deutsch), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Die Kugel wurde auf einen seltsamen [color:65845]Thron[/color] platziert.[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Was ist dein Lieblingsvideospiel und warum?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 Wörter</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18623,7 +19884,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18635,7 +19896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -18988,7 +20249,7 @@
     <row r="22" ht="84" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -19010,7 +20271,7 @@
     <row r="23" ht="84" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -19032,7 +20293,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -19054,7 +20315,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -19076,7 +20337,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -19098,7 +20359,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -19118,47 +20379,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Italiano), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]L'orba è stata piazzata su uno strano [color:65845]trono[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Qual è il tuo videogioco preferito, dicci perché?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 parole</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -19166,7 +20463,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19178,7 +20475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -19531,7 +20828,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -19553,7 +20850,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -19575,7 +20872,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -19597,7 +20894,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -19619,7 +20916,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -19641,7 +20938,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -19661,47 +20958,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Nederlands), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]De bol werd op een vreemde [color:65845]troon[/color] geplaatst.[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Wat is je favoriete videogame, vertel ons waarom?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 woorden</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -19709,7 +21042,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19721,7 +21054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -20074,7 +21407,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -20096,7 +21429,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -20118,7 +21451,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -20140,7 +21473,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -20162,7 +21495,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -20184,7 +21517,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -20204,47 +21537,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Svenska), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Klotet placerades på en sällsam [color:65845]tron[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Vilket är ditt favoritvideospel, berätta varför?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 ord</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -20252,7 +21621,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20264,7 +21633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -20617,7 +21986,7 @@
     <row r="22" ht="42" customHeight="1" s="9">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -20639,7 +22008,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -20661,7 +22030,7 @@
     <row r="24" ht="28" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -20683,7 +22052,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -20705,7 +22074,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -20727,7 +22096,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -20747,47 +22116,83 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="9">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Norsk), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Kulen ble plassert på en sær [color:65845]trone[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="9">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Hva er favorittvideospillet ditt, fortell oss hvorfor?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>250 ord</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -20795,7 +22200,7 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20807,7 +22212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="9" min="1" max="1"/>
@@ -21186,7 +22591,7 @@
     <row r="23" ht="42" customHeight="1" s="9">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.referenceEN</t>
+          <t>proofreading.q2-1.referenceEN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -21208,7 +22613,7 @@
     <row r="24" ht="42" customHeight="1" s="9">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q5.target</t>
+          <t>proofreading.q2-1.target</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -21230,7 +22635,7 @@
     <row r="25" ht="28" customHeight="1" s="9">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.referenceEN</t>
+          <t>proofreading.q2-2.referenceEN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -21252,7 +22657,7 @@
     <row r="26" ht="28" customHeight="1" s="9">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q6.target</t>
+          <t>proofreading.q2-2.target</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -21274,7 +22679,7 @@
     <row r="27" ht="28" customHeight="1" s="9">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.referenceEN</t>
+          <t>proofreading.q2-3.referenceEN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -21296,7 +22701,7 @@
     <row r="28" ht="28" customHeight="1" s="9">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>proofreading.q7.target</t>
+          <t>proofreading.q2-3.target</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -21316,55 +22721,91 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="9">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>proofreading.q2-4.referenceEN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE text (English), LEFT column of the table — Q2-4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT]</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>proofreading.q2-4.target</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TARGET text (Dansk), RIGHT column of the table — Q2-4 (EN ref.: [KIT]The orb was placed on a strange [color:65845]throne[/color].[/KIT])</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>[KIT]Kuglen blev placeret på en særegen [color:65845]trone[/color].[KIT]</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" s="9">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PAGE 4 — Section C: Q9 writing prompt + word-count suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>writingPrompt.q9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Translated/adapted Q9 prompt (replaces the HTML default text)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Hvad er dit yndlingsvideospil, og fortæl os hvorfor?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>wordCount.suffixLabel</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Suffix shown after the Q9 prompt (e.g. '(250 words)')</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>250 ord</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
